--- a/output/2026-10-04_23_Malesia_Selangor_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_23_Malesia_Selangor_Utensilerie_e_Macchine_Utensili.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Macchine per lavorazione lamiera (torni, frese, punzonatrici, laser, waterjet, piegatrici). Dal 1983. Verificata via sito ufficiale.</t>
+          <t>Macchine per lavorazione lamiera (torni, frese, punzonatrici, laser, waterjet, piegatrici). Dal 1983. Verificata via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -520,7 +520,6 @@
           <t>Numac Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Petaling Jaya, Selangor</t>
@@ -531,11 +530,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Macchine utensili CNC, lamiera, laser, EDM, forni trattamento termico. Dal 1985, filiali Penang/Johor. Verificata via machinetools.com.</t>
+          <t>Macchine utensili CNC, lamiera, laser, EDM, forni trattamento termico. Dal 1985, filiali Penang/Johor. Verificata via machinetools.com. [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -550,7 +547,6 @@
           <t>V-Tech Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Puchong, Selangor</t>
@@ -561,8 +557,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>CNC lathes, machining centers, EDM sinker, laser cutters. Dal 1994. Verificata via machinetools.com.</t>
@@ -570,7 +564,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +574,6 @@
           <t>Dynarco Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Puchong Utama, Selangor</t>
@@ -591,11 +584,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CNC lathes, centri di lavorazione, fresatrici. Dal 1986. Verificata via machinetools.com + jobstore.my.</t>
+          <t>CNC lathes, centri di lavorazione, fresatrici. Dal 1986. Verificata via machinetools.com + jobstore.my. [DUPLICATO — vedi anche: 2026-10-04_14_Malesia_Pulau_Pinang_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -610,7 +601,6 @@
           <t>MEP Solutions Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Seri Kembangan, Selangor</t>
@@ -621,11 +611,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mitsubishi Wire Cut &amp; Sinker EDM, laser cutting, Yougar Superdrill, Deratech press brake/turret punch. Verificata via machinetools.com.</t>
+          <t>Mitsubishi Wire Cut &amp; Sinker EDM, laser cutting, Yougar Superdrill, Deratech press brake/turret punch. Verificata via machinetools.com. [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -655,11 +643,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Macchine CNC giapponesi, utensileria, consumabili. Dal 1990, distributore ufficiale Takisawa. Sito non raggiungibile via fetch diretto, verificata via fonti indipendenti.</t>
+          <t>Macchine CNC giapponesi, utensileria, consumabili. Dal 1990, distributore ufficiale Takisawa. Sito non raggiungibile via fetch diretto, verificata via fonti indipendenti. [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -694,7 +680,6 @@
           <t>+603-5569 7877</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Dealer autorizzato HAAS Automation (HFO), SolidCAM, Fanuc. Verificata via fetch diretto sito + jobstore.my. Nota: sito presentava contenuti promozionali estranei iniettati (possibile compromissione minore), non inficia esistenza azienda.</t>
@@ -702,7 +687,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -712,7 +697,6 @@
           <t>CBA Industries Sdn Bhd</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Petaling Jaya, Selangor</t>
@@ -723,8 +707,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Distributore abrasivi Norton Abrasives, Ridgid Tool, Simple Green. Dal 1974. Verificata via maukerja.my.</t>
@@ -732,7 +714,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -769,7 +751,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Utensili industriali, torque tools, sollevamento. Dal 1984, reg. SSM 198401019077. Verificata via fetch diretto sito ufficiale.</t>
+          <t>Utensili industriali, torque tools, sollevamento. Dal 1984, reg. SSM 198401019077. Verificata via fetch diretto sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -799,8 +781,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Abrasivi, utensili manuali. Verificata su Lapasar (B2B verified supplier). Nessun sito proprio reperito.</t>
@@ -833,11 +813,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Utensili manuali, elettroutensili, strumenti di misura, saldatura. Dal 2007. Verificata via lapasar.com + machinetools.com (come 'Technotools'); fetch diretto bloccato da rate-limit (429).</t>
+          <t>Utensili manuali, elettroutensili, strumenti di misura, saldatura. Dal 2007. Verificata via lapasar.com + machinetools.com (come 'Technotools'); fetch diretto bloccato da rate-limit (429). [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perlis_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -872,10 +850,9 @@
           <t>+60 3-5614 1254</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Utensili da taglio rotanti di precisione. Filiale gruppo tedesco, dal 2006. Verificata via AHK Malaysia (Camera Commercio Malese-Tedesca) + info-clipper.com.</t>
+          <t>Utensili da taglio rotanti di precisione. Filiale gruppo tedesco, dal 2006. Verificata via AHK Malaysia (Camera Commercio Malese-Tedesca) + info-clipper.com. [DUPLICATO — vedi anche: 2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -890,7 +867,6 @@
           <t>TSIS Welding Solutions Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Klang, Selangor</t>
@@ -901,8 +877,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Distributore esclusivo Fronius Perfect Welding Malesia, saldatura MIG/TIG/robotica (ABB/Motoman/KUKA). Dal 2015. Verificata via hiredly.com, maukerja.my, jobstreet.com.my. Categoria: Saldatura (adiacente).</t>
@@ -910,7 +884,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -920,7 +894,6 @@
           <t>W E Sales &amp; Service Sdn Bhd (WESS)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Seri Kembangan, Selangor</t>
@@ -931,8 +904,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Macchine saldatura marchio proprio (Mello, Wess, PNL-tec, Eco-weld, Konfot), distributore esclusivo Lamello AG. Dal 1999. Verificata via maukerja.my, datanyze.com, owler.com. Categoria: Saldatura (adiacente).</t>
@@ -940,7 +911,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -950,7 +921,6 @@
           <t>Weld Systems Sdn Bhd</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Petaling Jaya, Selangor</t>
@@ -961,11 +931,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Vendita/noleggio/riparazione saldatrici (CO2, MIG, TIG, subarc, plasma) e ricambi. Verificata via jobstore.my. Categoria: Saldatura (adiacente).</t>
+          <t>Vendita/noleggio/riparazione saldatrici (CO2, MIG, TIG, subarc, plasma) e ricambi. Verificata via jobstore.my. Categoria: Saldatura (adiacente). [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -980,7 +948,6 @@
           <t>Mechkinarc (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Shah Alam, Selangor</t>
@@ -991,11 +958,9 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Agente esclusivo saldatrici MORROW Inverter IGBT. Verificata via machinetools.com (pagina brand Mechkinarc). Categoria: Saldatura (adiacente).</t>
+          <t>Agente esclusivo saldatrici MORROW Inverter IGBT. Verificata via machinetools.com (pagina brand Mechkinarc). Categoria: Saldatura (adiacente). [DUPLICATO — vedi anche: 2026-10-04_21_Malesia_Selangor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1042,7 +1007,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1037,6 @@
           <t>03-5569 7077</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Distribuzione pneumatica, idraulica, meccatronica, tecnologia ambientale. Verificata via sgpgrid.com + sito ufficiale. ATTENZIONE: categoria pneumatica/idraulica, non utensileria/macchine utensili in senso stretto - valutare se in target.</t>
@@ -1080,7 +1044,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1069,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>sales@unipacstore.com</t>
@@ -1118,7 +1081,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1118,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Distribuzione componenti pneumatici. Dal 1978. Verificata via lapasar.com + plantautomation-technology.com. ATTENZIONE: e' filiale diretta multinazionale (produttore/brand), non distributore terzo in senso classico; categoria pneumatica, non utensileria/macchine utensili in senso stretto.</t>
+          <t>Distribuzione componenti pneumatici. Dal 1978. Verificata via lapasar.com + plantautomation-technology.com. ATTENZIONE: e' filiale diretta multinazionale (produttore/brand), non distributore terzo in senso classico; categoria pneumatica, non utensileria/macchine utensili in senso stretto. [DUPLICATO — vedi anche: 2026-10-03_08_Malesia_Perak_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
